--- a/ETF/Quantities2.xlsx
+++ b/ETF/Quantities2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1001"/>
+  <dimension ref="A1:C1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11451,6 +11451,28 @@
         <v>2744.15</v>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1002" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1003" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Quantities2.xlsx
+++ b/ETF/Quantities2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1003"/>
+  <dimension ref="A1:C1013"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11473,6 +11473,116 @@
         <v>2744.15</v>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1004" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1005" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1006" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1007" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1008" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1009" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1010" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1013" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Quantities2.xlsx
+++ b/ETF/Quantities2.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1013"/>
+  <dimension ref="A1:C1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11583,6 +11583,94 @@
         <v>2744.15</v>
       </c>
     </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1014" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1015" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1016" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1017" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1018" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1019" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1020" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1021" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Quantities2.xlsx
+++ b/ETF/Quantities2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1021"/>
+  <dimension ref="A1:C1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11671,6 +11671,17 @@
         <v>2744.15</v>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1022" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ETF/Quantities2.xlsx
+++ b/ETF/Quantities2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1022"/>
+  <dimension ref="A1:C1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11682,6 +11682,94 @@
         <v>2744.15</v>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1023" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1024" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1025" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1026" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1027" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1028" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1029" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1030" t="n">
+        <v>20.5516</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>2744.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
